--- a/output/pdf_financials_xlsx/PSLV.U.xlsx
+++ b/output/pdf_financials_xlsx/PSLV.U.xlsx
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>53.898</v>
+        <v>60.536</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>84.015</v>
+        <v>87.114</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>118.606</v>
+        <v>119.455</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>131.333</v>
+        <v>120.103</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>148.815</v>
+        <v>101.076</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>174.111</v>
+        <v>109.649</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>217.441</v>
+        <v>194.724</v>
       </c>
     </row>
     <row r="11">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19.588</v>
+        <v>12.95</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>37.761</v>
+        <v>34.662</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46.039</v>
+        <v>45.19</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>13.849</v>
+        <v>25.079</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.552</v>
+        <v>50.291</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4.544</v>
+        <v>69.006</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>67.64100000000001</v>
+        <v>90.358</v>
       </c>
     </row>
     <row r="12">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E324" s="5" t="n">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E328" s="5" t="n">

--- a/output/pdf_financials_xlsx/PSLV.U.xlsx
+++ b/output/pdf_financials_xlsx/PSLV.U.xlsx
@@ -1211,25 +1211,25 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>2.916</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>3.183</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>3.622</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>3.355</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>2.221</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>2.477</v>
       </c>
     </row>
     <row r="29">
@@ -1239,25 +1239,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.527</v>
+        <v>4.443</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>30.706</v>
+        <v>33.889</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>41.655</v>
+        <v>45.277</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20.088</v>
+        <v>23.443</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>43.8</v>
+        <v>46.643</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>60.097</v>
+        <v>62.318</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>83.696</v>
+        <v>86.173</v>
       </c>
     </row>
     <row r="30">
@@ -1267,25 +1267,25 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.077946819802411</v>
+        <v>6.046049587676564</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>25.21514912626462</v>
+        <v>27.82896465641834</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>25.29988763703726</v>
+        <v>27.49977223723769</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>13.83642600322354</v>
+        <v>16.14731853811078</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>28.93629390818342</v>
+        <v>30.81451042829679</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>33.63857714589572</v>
+        <v>34.88175533850158</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>29.35857051655313</v>
+        <v>30.22744333209392</v>
       </c>
     </row>
     <row r="31">
@@ -3226,16 +3226,16 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>3.355</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2.221</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.477</v>
       </c>
     </row>
     <row r="101">
@@ -17723,7 +17723,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -20282,7 +20286,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -21154,7 +21162,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -21530,7 +21542,11 @@
           <t>Depreciation of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E351" s="5" t="n">
         <v>2.916</v>
       </c>

--- a/output/pdf_financials_xlsx/PSLV.U.xlsx
+++ b/output/pdf_financials_xlsx/PSLV.U.xlsx
@@ -17772,7 +17772,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E269" s="5" t="n">
         <v>0.231</v>
       </c>
